--- a/output/pdf_financials_xlsx/VZLA.xlsx
+++ b/output/pdf_financials_xlsx/VZLA.xlsx
@@ -883,10 +883,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.044461</v>
+        <v>-0.044461</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.889732</v>
+        <v>-0.889732</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>4.211897</v>
@@ -920,7 +920,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.004867</v>
+        <v>-8.418927</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-22.198544</v>
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.044461</v>
+        <v>-0.044461</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.889732</v>
+        <v>-0.889732</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4.20703</v>
+        <v>-4.20703</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-11.099272</v>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.044461</v>
+        <v>-0.044461</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.889732</v>
+        <v>-0.889732</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4.20703</v>
+        <v>-4.20703</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-11.099272</v>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>38.245727</v>
+        <v>-38.245727</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>85.379015</v>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.044461</v>
+        <v>-0.044461</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.889732</v>
+        <v>-0.889732</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>4.211897</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.044461</v>
+        <v>-0.044461</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.889732</v>
+        <v>-0.889732</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>4.216953</v>
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.1155536329592105</v>
+        <v>199.8844463670408</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>200</v>
@@ -3330,25 +3330,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.288466</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.126899</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>8.14873</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>23.691609</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>30.324553</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>36.57286</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>45.456805</v>
       </c>
     </row>
     <row r="93">
@@ -4115,19 +4115,19 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-2.009743</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-11.7978</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>-18.73154</v>
+        <v>-46.079993</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>-5.169327</v>
+        <v>-35.917865</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>-0.272492</v>
+        <v>-33.435521</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0</v>
@@ -6042,7 +6042,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -8866,7 +8870,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -11826,7 +11834,11 @@
           <t>Exploration and evaluation expenditures 7a</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -13318,7 +13330,11 @@
           <t>Exploration and evaluation expenditures 9</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -14468,7 +14484,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -21148,7 +21168,7 @@
         </is>
       </c>
       <c r="G297" s="5" t="n">
-        <v>4.20703</v>
+        <v>-4.20703</v>
       </c>
       <c r="H297" s="5" t="n">
         <v>-11.099272</v>
@@ -22205,10 +22225,10 @@
         </is>
       </c>
       <c r="F316" s="5" t="n">
-        <v>0.889732</v>
+        <v>-0.889732</v>
       </c>
       <c r="G316" s="5" t="n">
-        <v>4.20703</v>
+        <v>-4.20703</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -22698,10 +22718,10 @@
         </is>
       </c>
       <c r="E325" s="5" t="n">
-        <v>0.044461</v>
+        <v>-0.044461</v>
       </c>
       <c r="F325" s="5" t="n">
-        <v>0.889732</v>
+        <v>-0.889732</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VZLA.xlsx
+++ b/output/pdf_financials_xlsx/VZLA.xlsx
@@ -768,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.03879</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.139864</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.95974</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>1.63296</v>
@@ -1269,13 +1269,13 @@
         <v>4.211897</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>11.099272</v>
+        <v>11.138062</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-15.270556</v>
+        <v>-15.41042</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-13.591728</v>
+        <v>-14.551468</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-17.581349</v>
@@ -1331,13 +1331,13 @@
         <v>4.216953</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>11.110375</v>
+        <v>11.149165</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-15.270556</v>
+        <v>-15.41042</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-13.591728</v>
+        <v>-14.551468</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-17.252373</v>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.090778</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.150222</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>2.58391</v>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.090778</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.150222</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>2.58391</v>
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.104102</v>
+        <v>0.013324</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.162047</v>
+        <v>0.011825</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.369287</v>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -21096,7 +21096,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">

--- a/output/pdf_financials_xlsx/VZLA.xlsx
+++ b/output/pdf_financials_xlsx/VZLA.xlsx
@@ -613,13 +613,13 @@
         <v>1.335678</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2.661812</v>
+        <v>2.904298</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.975187</v>
+        <v>4.376993</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>4.72388</v>
+        <v>5.04843</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.883141</v>
@@ -886,7 +886,7 @@
         <v>-0.044461</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.889732</v>
+        <v>-0.939797</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>4.211897</v>
@@ -917,10 +917,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>0.050065</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-8.418927</v>
+        <v>0.004867</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-22.198544</v>
@@ -1263,7 +1263,7 @@
         <v>-0.044461</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.889732</v>
+        <v>-0.939797</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>4.211897</v>
@@ -1325,7 +1325,7 @@
         <v>-0.044461</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.889732</v>
+        <v>-0.939797</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>4.216953</v>
@@ -1403,10 +1403,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-5.327214281382043</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>199.8844463670408</v>
+        <v>0.1155536329592105</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>200</v>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000775</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.022924</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>-0.239244</v>
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.005624</v>
+        <v>0.004849</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.028786</v>
+        <v>0.005862</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.294099</v>
@@ -3898,19 +3898,19 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.041616</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.073125</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.280478</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.285852</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.503177</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -4627,19 +4627,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.041616</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.073125</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.280478</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.285852</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.503177</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -4658,19 +4658,19 @@
         <v>-0.223657</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-3.03181</v>
+        <v>-3.073426</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-6.39318</v>
+        <v>-6.466305</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-14.179264</v>
+        <v>-14.459742</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-12.308821</v>
+        <v>-12.594673</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-14.483699</v>
+        <v>-14.986876</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-6.990576</v>
@@ -11950,7 +11950,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -13388,7 +13392,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -14540,7 +14548,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -17030,7 +17042,11 @@
           <t>Deferred tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -17256,7 +17272,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E226" s="5" t="n">
         <v>-0.000775</v>
       </c>
@@ -19170,7 +19190,11 @@
           <t>Directors fees 8</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -20096,7 +20120,11 @@
           <t>Directors fees 11</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -20706,7 +20734,11 @@
           <t>Directors fees 10</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -21652,7 +21684,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -22160,7 +22196,11 @@
           <t>Income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
